--- a/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.044273542233032</v>
+        <v>-2.3813509957563435</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.4401561292253504</v>
+        <v>-2.823333920920216</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.6483909552407134</v>
+        <v>-1.939368070592471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.20198091173077468</v>
+        <v>0.22550149243054726</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4527941679615175E-24</v>
+        <v>4.55471740722439E-26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.12947421336914858</v>
+        <v>0.09242562649602964</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08714724416803743</v>
+        <v>0.05940755210262894</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19235917426414847</v>
+        <v>0.14379478922858277</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4153021307577833</v>
+        <v>0.47946341985028185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.25078866271447064</v>
+        <v>0.28811156096547</v>
       </c>
       <c r="E2" t="n">
-        <v>0.579815598801096</v>
+        <v>0.6708152787350936</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08393544287924118</v>
+        <v>0.09762849943102644</v>
       </c>
       <c r="G2" t="n">
-        <v>7.502782742392063E-7</v>
+        <v>9.056642703106504E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.514828347796608</v>
+        <v>1.6152074813552657</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2850384790880776</v>
+        <v>1.333906107676115</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7857091134863368</v>
+        <v>1.9558312184139766</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3881997981747609</v>
+        <v>0.46912474226450146</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1397043335054848</v>
+        <v>0.1791490399906837</v>
       </c>
       <c r="E2" t="n">
-        <v>0.636695262844037</v>
+        <v>0.7591004445383192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1267834003414674</v>
+        <v>0.1479467868743968</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0021992703669632056</v>
+        <v>0.0015196647280992129</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4743243221716715</v>
+        <v>1.5985943986028885</v>
       </c>
       <c r="I2" t="n">
-        <v>1.149933751708138</v>
+        <v>1.1961990123726676</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8902238530856195</v>
+        <v>2.13635358733132</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3692237171868319</v>
+        <v>-0.25109529814607673</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.658261170688057</v>
+        <v>-0.5909261414206313</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.08018626368560677</v>
+        <v>0.08873554512847781</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1474680885210332</v>
+        <v>0.17338308330334415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.012288367485654204</v>
+        <v>0.14755803351340316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6912707440039947</v>
+        <v>0.7779482310021264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.517750832552189</v>
+        <v>0.5538141369359227</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9229444193460932</v>
+        <v>1.0927916240414803</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04911703274494663</v>
+        <v>0.12503159606164435</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.17259091432156834</v>
+        <v>-0.004909195161544561</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0743568488316751</v>
+        <v>0.2549723872848333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06299687835541924</v>
+        <v>0.0662963220526474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.43558274336106884</v>
+        <v>0.059301596246021014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9520696998478076</v>
+        <v>1.133184256660825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8414817825886941</v>
+        <v>0.9951028352424377</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0771911313157325</v>
+        <v>1.2904259882156788</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4924858584095381</v>
+        <v>0.6995302942387835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.29048860973470786</v>
+        <v>0.4617602761885117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6944831070843684</v>
+        <v>0.9373003122890554</v>
       </c>
       <c r="F2" t="n">
-        <v>0.10305982075246442</v>
+        <v>0.12131123369911831</v>
       </c>
       <c r="G2" t="n">
-        <v>1.764842062716888E-6</v>
+        <v>8.097798821989244E-9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6363789745820114</v>
+        <v>2.0128070583279234</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3370806390608352</v>
+        <v>1.5868648483356098</v>
       </c>
       <c r="J2" t="n">
-        <v>2.002673638543533</v>
+        <v>2.5530795885383872</v>
       </c>
     </row>
   </sheetData>
